--- a/history/아시아종목.xlsx
+++ b/history/아시아종목.xlsx
@@ -970,7 +970,11 @@
           <t>MiniMax</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>0100.HK</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -1058,7 +1062,11 @@
           <t>China Hongqiao Group</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>1378.HK</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -1652,7 +1660,11 @@
           <t>Kingboard Holdings</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>0148.HK</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -1717,7 +1729,11 @@
           <t>Yue Yuen Industrial</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>0551.HK</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t>홍콩</t>
@@ -1828,7 +1844,11 @@
           <t>Yankuang Energy H</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>1171.HK</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -1847,7 +1867,11 @@
           <t>Hysan Development</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>0014.HK</t>
+        </is>
+      </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>홍콩</t>
@@ -1981,7 +2005,11 @@
           <t>Hang Lung Properties</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>0101.HK</t>
+        </is>
+      </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t>홍콩</t>
@@ -2000,7 +2028,11 @@
           <t>COSCO Shipping H</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>1919.HK</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2019,7 +2051,11 @@
           <t>VTech Holdings</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>0303.HK</t>
+        </is>
+      </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
           <t>홍콩</t>
@@ -2040,7 +2076,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>OOIL</t>
+          <t>0316.HK</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2061,7 +2097,11 @@
           <t>Sino Land</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>0083.HK</t>
+        </is>
+      </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
           <t>홍콩</t>
@@ -2126,7 +2166,11 @@
           <t>SITC International</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2145,7 +2189,11 @@
           <t>Far East Horizon</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr"/>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>3360.HK</t>
+        </is>
+      </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2187,7 +2235,11 @@
           <t>PetroChina H</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>0857.HK</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2229,7 +2281,11 @@
           <t>C&amp;D International Investment</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr"/>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>1908.HK</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2271,7 +2327,11 @@
           <t>CNOOC</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>0883.HK</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2290,7 +2350,11 @@
           <t>Henderson Land</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>0012.HK</t>
+        </is>
+      </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
           <t>홍콩</t>
@@ -2355,7 +2419,11 @@
           <t>China Everbright Environment</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>0257.HK</t>
+        </is>
+      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2374,7 +2442,11 @@
           <t>Kerry Properties</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>0683.HK</t>
+        </is>
+      </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
           <t>홍콩</t>
@@ -2416,7 +2488,11 @@
           <t>WH Group</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr"/>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>0288.HK</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2435,7 +2511,11 @@
           <t>China Shenhua Energy H</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr"/>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>1088.HK</t>
+        </is>
+      </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2500,7 +2580,11 @@
           <t>Vishal Mega Mart</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr"/>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>VMM.NS</t>
+        </is>
+      </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
           <t>인도</t>
@@ -2772,7 +2856,11 @@
           <t>BeOne Medicines</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr"/>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>6160.HK</t>
+        </is>
+      </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -2998,7 +3086,11 @@
           <t>Horiba</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr"/>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>6856.T</t>
+        </is>
+      </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3132,7 +3224,11 @@
           <t>Tokyo Seimitsu</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr"/>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>7729.T</t>
+        </is>
+      </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3383,7 +3479,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>TATAMOTORS.NS</t>
+          <t>TMPV.NS</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -3427,7 +3523,11 @@
           <t>Fujikura</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3469,7 +3569,11 @@
           <t>Knowledge Atlas</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr"/>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>688787.SS</t>
+        </is>
+      </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -3511,7 +3615,11 @@
           <t>ULVAC</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr"/>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>6728.T</t>
+        </is>
+      </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3645,7 +3753,11 @@
           <t>Socionext</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr"/>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>6526.T</t>
+        </is>
+      </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3687,7 +3799,11 @@
           <t>Macnica Holdings</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr"/>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>3132.T</t>
+        </is>
+      </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3752,7 +3868,11 @@
           <t>Micronics Japan</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr"/>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>6871.T</t>
+        </is>
+      </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3840,7 +3960,11 @@
           <t>RORZE</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr"/>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>6323.T</t>
+        </is>
+      </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3859,7 +3983,11 @@
           <t>CG Power &amp; Industrial</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>CGPOWER.NS</t>
+        </is>
+      </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
           <t>인도</t>
@@ -3901,7 +4029,11 @@
           <t>Alps Alpine</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr"/>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>6770.T</t>
+        </is>
+      </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -3920,7 +4052,11 @@
           <t>Wuhan Jingce Electronic</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr"/>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>300567.SZ</t>
+        </is>
+      </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -3962,7 +4098,11 @@
           <t>ABB India</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr"/>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>ABB.NS</t>
+        </is>
+      </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
           <t>인도</t>
@@ -3981,7 +4121,11 @@
           <t>Shanghai BOCHU Electronic</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr"/>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>688188.SS</t>
+        </is>
+      </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -4023,7 +4167,11 @@
           <t>RoboTechnik Intelligent</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr"/>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>301021.SZ</t>
+        </is>
+      </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -4065,7 +4213,11 @@
           <t>Rigaku Holdings</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr"/>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>268A.T</t>
+        </is>
+      </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -4107,7 +4259,11 @@
           <t>Hindalco Industries</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr"/>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>HINDALCO.NS</t>
+        </is>
+      </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
           <t>인도</t>
@@ -4126,7 +4282,11 @@
           <t>Shibaura Mechatronics</t>
         </is>
       </c>
-      <c r="C166" s="3" t="inlineStr"/>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>6590.T</t>
+        </is>
+      </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
           <t>일본</t>
@@ -4145,7 +4305,11 @@
           <t>Pidilite Industries</t>
         </is>
       </c>
-      <c r="C167" s="3" t="inlineStr"/>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND.NS</t>
+        </is>
+      </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
           <t>인도</t>
@@ -4187,7 +4351,11 @@
           <t>JSW Steel</t>
         </is>
       </c>
-      <c r="C169" s="3" t="inlineStr"/>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>JSWSTEEL.NS</t>
+        </is>
+      </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
           <t>인도</t>
@@ -4206,7 +4374,11 @@
           <t>Aditya Infotech</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr"/>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>CPPLUS.NS</t>
+        </is>
+      </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
           <t>인도</t>
@@ -4271,7 +4443,11 @@
           <t>SUPCON Technology</t>
         </is>
       </c>
-      <c r="C173" s="3" t="inlineStr"/>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>688777.SS</t>
+        </is>
+      </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
           <t>중국</t>
@@ -4336,7 +4512,11 @@
           <t>Tekscend Photomask</t>
         </is>
       </c>
-      <c r="C176" s="3" t="inlineStr"/>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>5357.T</t>
+        </is>
+      </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
           <t>일본</t>
